--- a/volunteer_registration_forms/018_disability_advocacy_network_registration_form--volunteer_registration_forms.xlsx
+++ b/volunteer_registration_forms/018_disability_advocacy_network_registration_form--volunteer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'hearing'}</t>
+          <t>hearing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Hearing'}</t>
+          <t>Hearing</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'speech'}</t>
+          <t>speech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Speech'}</t>
+          <t>Speech</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'mobility'}</t>
+          <t>mobility</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Mobility'}</t>
+          <t>Mobility</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'visual'}</t>
+          <t>visual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Visual'}</t>
+          <t>Visual</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cognitive'}</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cognitive'}</t>
+          <t>Cognitive</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Mental health'}</t>
+          <t>Mental health</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'prophets'}</t>
+          <t>prophets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'prophets'}</t>
+          <t>prophets</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'arts_and_culture'}</t>
+          <t>arts_and_culture</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Arts and culture'}</t>
+          <t>Arts and culture</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'employment'}</t>
+          <t>employment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Employment'}</t>
+          <t>Employment</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'health_and_wellness'}</t>
+          <t>health_and_wellness</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Health and wellness'}</t>
+          <t>Health and wellness</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'housing_and_transportation'}</t>
+          <t>housing_and_transportation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Housing and transportation'}</t>
+          <t>Housing and transportation</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'income_and_financial'}</t>
+          <t>income_and_financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Income and financial'}</t>
+          <t>Income and financial</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'legal_and_advocacy'}</t>
+          <t>legal_and_advocacy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Legal and advocacy'}</t>
+          <t>Legal and advocacy</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'living_and_social'}</t>
+          <t>living_and_social</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Living and social'}</t>
+          <t>Living and social</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
